--- a/resources/templates/standard/F2100-04.xlsx
+++ b/resources/templates/standard/F2100-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">자격인증 변경
 요청서</t>
@@ -567,12 +570,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -585,30 +590,30 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4"/>
@@ -681,7 +686,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -698,7 +703,7 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -718,7 +723,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -753,7 +758,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -770,7 +775,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
@@ -790,7 +795,7 @@
     </row>
     <row r="7" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -807,7 +812,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
@@ -827,7 +832,7 @@
     </row>
     <row r="8" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -862,7 +867,7 @@
     </row>
     <row r="9" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -1194,7 +1199,7 @@
     </row>
     <row r="19" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1229,7 +1234,7 @@
     </row>
     <row r="20" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1246,7 +1251,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
@@ -1266,7 +1271,7 @@
     </row>
     <row r="21" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1283,7 +1288,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
@@ -1303,7 +1308,7 @@
     </row>
     <row r="22" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1338,7 +1343,7 @@
     </row>
     <row r="23" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1670,13 +1675,13 @@
     </row>
     <row r="33" ht="20.15" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -1711,7 +1716,7 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
